--- a/docs/data/jp/xlsx/9206.xlsx
+++ b/docs/data/jp/xlsx/9206.xlsx
@@ -7169,7 +7169,7 @@
     <row r="86">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>Business Expenses COSExp OA</t>
+          <t>사업비</t>
         </is>
       </c>
       <c r="D86" s="22" t="n">
@@ -7717,7 +7717,7 @@
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Sales Of Goods NOI</t>
+          <t>저장품 매각 수입</t>
         </is>
       </c>
       <c r="C96" s="22" t="n">
@@ -8230,7 +8230,7 @@
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
         <is>
-          <t>Loss On Sales Of Supplies NOE</t>
+          <t>저장품 매각 손실</t>
         </is>
       </c>
       <c r="C105" s="22" t="n">
@@ -8600,7 +8600,7 @@
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>Reversal Of Reserve For Scheduled Maintenance Costs EI</t>
+          <t>정기 정비 충당금 환입액</t>
         </is>
       </c>
       <c r="T112" s="22" t="n">
@@ -8827,7 +8827,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>Income Before Income Taxes</t>
+          <t>법인세 차감 전 중간 순이익 또는 순손실(△)</t>
         </is>
       </c>
       <c r="C121" s="12" t="n">
@@ -9495,7 +9495,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>Income Before Income Taxes</t>
+          <t>법인세 차감 전 중간 순이익 또는 순손실(△)</t>
         </is>
       </c>
       <c r="D132" s="12" t="n">
@@ -9660,7 +9660,7 @@
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Reserve For Scheduled Maintenance Costs Ope CF</t>
+          <t>정기 정비 충당금 증감액(△는 감소)</t>
         </is>
       </c>
       <c r="D135" s="22" t="n">
@@ -9731,7 +9731,7 @@
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Scheduled Maintenance Costs Ope CF</t>
+          <t>정기 정비 충당금 증감액(△는 감소)</t>
         </is>
       </c>
       <c r="F137" s="22" t="n">
@@ -11299,7 +11299,7 @@
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Restoration Of Guarantee Deposits Inv CF</t>
+          <t>차입 보증금 반환 수입</t>
         </is>
       </c>
       <c r="D172" s="22" t="n">
@@ -14905,7 +14905,7 @@
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>Derivatives CA</t>
+          <t>파생상품 자산</t>
         </is>
       </c>
       <c r="E78" s="22" t="n">
@@ -15197,7 +15197,7 @@
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>Aircraft Parts PPE</t>
+          <t>항공기재</t>
         </is>
       </c>
       <c r="E88" s="22" t="n">
@@ -15247,7 +15247,7 @@
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>Aircraft Parts Net PPE</t>
+          <t>항공기재(순액)</t>
         </is>
       </c>
       <c r="E90" s="22" t="n">
@@ -15572,7 +15572,7 @@
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
-          <t>Aircraft Net</t>
+          <t>항공기재(순액)</t>
         </is>
       </c>
       <c r="C103" s="22" t="n">
@@ -16410,7 +16410,7 @@
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>Derivatives Liabilities CL</t>
+          <t>파생상품 부채</t>
         </is>
       </c>
       <c r="H131" s="22" t="n">
@@ -16593,7 +16593,7 @@
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>Reserve For Scheduled Maintenance Costs NCL</t>
+          <t>정기 정비 충당금</t>
         </is>
       </c>
       <c r="D137" s="22" t="n">
@@ -16649,7 +16649,7 @@
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>Provision For Scheduled Maintenance Costs NCL</t>
+          <t>정기 정비 충당금</t>
         </is>
       </c>
       <c r="C139" s="22" t="n">
